--- a/보장진단_한은주.xlsx
+++ b/보장진단_한은주.xlsx
@@ -4612,7 +4612,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>한은주 · 자동분석 2026.07.02</t>
+          <t>한은주 · 자동분석 2026.07.03</t>
         </is>
       </c>
     </row>
